--- a/per-stock/CSCO/financials.xlsx
+++ b/per-stock/CSCO/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>466916868096</v>
+        <v>471159111680</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>481828929536</v>
+        <v>487520108544</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>39.40333</v>
+        <v>39.84667</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24.934664</v>
+        <v>25.027584</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7.686381</v>
+        <v>7.7562165</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -606,7 +615,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.64276004</v>
+        <v>0.64296997</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -621,7 +630,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.25035998</v>
+        <v>0.24992001</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -696,7 +705,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31303000064</v>
+        <v>33001000960</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9671874560</v>
+        <v>11788000000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -726,7 +735,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3949893042</v>
+        <v>3941434665</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>118.21</v>
+        <v>119.54</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-07-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-04-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D51</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C51</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B51</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B51:E51)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D49</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C49</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B49</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B49:E49)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D38</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C38</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B38</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B38:E38)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B7:E7)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D4</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C4</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B4</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B4</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D2/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C2/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1801,7 +2281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1827,32 +2307,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>2024-10-31</t>
         </is>
       </c>
     </row>
@@ -1862,21 +2342,21 @@
           <t>Tax Effect Of Unusual Items</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n">
+      <c r="B2" s="3" t="n">
+        <v>44356028.71998</v>
+      </c>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n">
         <v>6733411.972869</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>8384128.042681</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>-13950000</v>
-      </c>
       <c r="F2" s="3" t="n">
+        <v>-13926026.467594</v>
+      </c>
+      <c r="G2" s="3" t="n">
         <v>-5723588.500173</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>-124320000</v>
       </c>
     </row>
     <row r="3">
@@ -1886,19 +2366,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.164892</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.129183</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.156591</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.149717</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>0.155</v>
-      </c>
       <c r="F3" s="3" t="n">
-        <v>0.158989</v>
+        <v>0.154734</v>
       </c>
       <c r="G3" s="3" t="n"/>
     </row>
@@ -1909,19 +2389,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>4784000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>4652000000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>4304000000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>3946000000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>4066000000</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>4088000000</v>
       </c>
       <c r="G4" s="3" t="n"/>
     </row>
@@ -1932,19 +2412,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>269000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>23000000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>43000000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>56000000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-90000000</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>-36000000</v>
       </c>
       <c r="G5" s="3" t="n"/>
     </row>
@@ -1955,19 +2435,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>269000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>23000000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>43000000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>56000000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-90000000</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-36000000</v>
       </c>
       <c r="G6" s="3" t="n"/>
     </row>
@@ -1978,19 +2458,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>3373000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>3175000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>2860000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>2550000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>2491000000</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>2428000000</v>
       </c>
       <c r="G7" s="3" t="n"/>
     </row>
@@ -2001,19 +2481,19 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>637000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>659000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>606000000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>635000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>626000000</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>761000000</v>
       </c>
       <c r="G8" s="3" t="n"/>
     </row>
@@ -2024,19 +2504,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>5352000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>4949000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>4763000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>5012000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>4489000000</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>4384000000</v>
       </c>
       <c r="G9" s="3" t="n"/>
     </row>
@@ -2047,19 +2527,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>5053000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>4675000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>4347000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>4002000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>3976000000</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>4052000000</v>
       </c>
       <c r="G10" s="3" t="n"/>
     </row>
@@ -2070,19 +2550,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>4416000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>4016000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>3741000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>3367000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>3350000000</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>3291000000</v>
       </c>
       <c r="G11" s="3" t="n"/>
     </row>
@@ -2093,19 +2573,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-163000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-160000000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-128000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-141000000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-153000000</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>-166000000</v>
       </c>
       <c r="G12" s="3" t="n"/>
     </row>
@@ -2116,19 +2596,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>377000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>370000000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>350000000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>368000000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>403000000</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>404000000</v>
       </c>
       <c r="G13" s="3" t="n"/>
     </row>
@@ -2139,19 +2619,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>214000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>210000000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>222000000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>227000000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>250000000</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>238000000</v>
       </c>
       <c r="G14" s="3" t="n"/>
     </row>
@@ -2162,19 +2642,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>3148356028.71998</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>3154971201.316511</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>2823733411.972869</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>2502384128.042681</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>2567050000</v>
-      </c>
       <c r="F15" s="3" t="n">
-        <v>2458276411.499827</v>
+        <v>2567073973.532406</v>
       </c>
       <c r="G15" s="3" t="n"/>
     </row>
@@ -2185,19 +2665,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>3373000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>3175000000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>2860000000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>2550000000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>2491000000</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>2428000000</v>
       </c>
       <c r="G16" s="3" t="n"/>
     </row>
@@ -2208,19 +2688,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>11882000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>11532000000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>11373000000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>11551000000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>10913000000</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>10868000000</v>
       </c>
       <c r="G17" s="3" t="n"/>
     </row>
@@ -2231,19 +2711,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>3960000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>3781000000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>3363000000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>3087000000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>3202000000</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>3113000000</v>
       </c>
       <c r="G18" s="3" t="n"/>
     </row>
@@ -2254,19 +2734,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>3982000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>3984000000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>3993000000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>3992000000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>4002000000</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>4005000000</v>
       </c>
       <c r="G19" s="3" t="n"/>
     </row>
@@ -2277,19 +2757,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>3952000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>3955000000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>3956000000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>3960000000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>3972000000</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>3981000000</v>
       </c>
       <c r="G20" s="3" t="n"/>
     </row>
@@ -2300,19 +2780,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>0.72</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>0.71</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>0.62</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>0.61</v>
       </c>
       <c r="G21" s="3" t="n"/>
     </row>
@@ -2323,19 +2803,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>0.72</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>0.71</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>0.63</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>0.61</v>
       </c>
       <c r="G22" s="3" t="n"/>
     </row>
@@ -2346,19 +2826,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>3373000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>3175000000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>2860000000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>2550000000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>2491000000</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>2428000000</v>
       </c>
       <c r="G23" s="3" t="n"/>
     </row>
@@ -2369,19 +2849,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>3373000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>3175000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>2860000000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>2550000000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>2491000000</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>2428000000</v>
       </c>
       <c r="G24" s="3" t="n"/>
     </row>
@@ -2392,19 +2872,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>3373000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>3175000000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>2860000000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>2550000000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>2491000000</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>2428000000</v>
       </c>
       <c r="G25" s="3" t="n"/>
     </row>
@@ -2415,19 +2895,19 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>3373000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>3175000000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>2860000000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>2550000000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>2491000000</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>2428000000</v>
       </c>
       <c r="G26" s="3" t="n"/>
     </row>
@@ -2438,19 +2918,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>3373000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>3175000000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>2860000000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>2550000000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>2491000000</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>2428000000</v>
       </c>
       <c r="G27" s="3" t="n"/>
     </row>
@@ -2461,19 +2941,19 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>666000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>471000000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>531000000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>449000000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>456000000</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>459000000</v>
       </c>
       <c r="G28" s="3" t="n"/>
     </row>
@@ -2484,19 +2964,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>4039000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>3646000000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>3391000000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>2999000000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>2947000000</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>2887000000</v>
       </c>
       <c r="G29" s="3" t="n"/>
     </row>
@@ -2507,19 +2987,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>243000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-11000000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>9000000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>18000000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-136000000</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>-70000000</v>
       </c>
       <c r="G30" s="3" t="n"/>
     </row>
@@ -2530,19 +3010,19 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-34000000</v>
+        <v>-26000000</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-34000000</v>
       </c>
       <c r="D31" s="3" t="n">
+        <v>-34000000</v>
+      </c>
+      <c r="E31" s="3" t="n">
         <v>-38000000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-46000000</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>-34000000</v>
       </c>
       <c r="G31" s="3" t="n"/>
     </row>
@@ -2553,19 +3033,19 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-36000000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>-147000000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>-35000000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>-34000000</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>-10000000</v>
       </c>
       <c r="G32" s="3" t="n"/>
     </row>
@@ -2576,19 +3056,19 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>36000000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>147000000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>35000000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>34000000</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>10000000</v>
       </c>
       <c r="G33" s="3" t="n"/>
     </row>
@@ -2599,19 +3079,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>268000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>59000000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>190000000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>91000000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>-56000000</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>-26000000</v>
       </c>
       <c r="G34" s="3" t="n"/>
     </row>
@@ -2622,19 +3102,19 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>-163000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-160000000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>-128000000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-141000000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>-153000000</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>-166000000</v>
       </c>
       <c r="G35" s="3" t="n"/>
     </row>
@@ -2645,19 +3125,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>377000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>370000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>350000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>368000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>403000000</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>404000000</v>
       </c>
       <c r="G36" s="3" t="n"/>
     </row>
@@ -2668,19 +3148,19 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>214000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>210000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>222000000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>227000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>250000000</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>238000000</v>
       </c>
       <c r="G37" s="3" t="n"/>
     </row>
@@ -2691,19 +3171,19 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>3959000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>3817000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>3510000000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>3122000000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>3236000000</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>3123000000</v>
       </c>
       <c r="G38" s="3" t="n"/>
     </row>
@@ -2714,19 +3194,19 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>6121000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>6155000000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>6235000000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>6158000000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>6042000000</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>5988000000</v>
       </c>
       <c r="G39" s="3" t="n"/>
     </row>
@@ -2737,19 +3217,19 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>231000000</v>
+        <v>228000000</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>231000000</v>
       </c>
       <c r="D40" s="3" t="n">
+        <v>231000000</v>
+      </c>
+      <c r="E40" s="3" t="n">
         <v>254000000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>244000000</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>265000000</v>
       </c>
       <c r="G40" s="3" t="n"/>
     </row>
@@ -2760,19 +3240,19 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>231000000</v>
+        <v>228000000</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>231000000</v>
       </c>
       <c r="D41" s="3" t="n">
+        <v>231000000</v>
+      </c>
+      <c r="E41" s="3" t="n">
         <v>254000000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>244000000</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>265000000</v>
       </c>
       <c r="G41" s="3" t="n"/>
     </row>
@@ -2783,19 +3263,19 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>231000000</v>
+        <v>228000000</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>231000000</v>
       </c>
       <c r="D42" s="3" t="n">
+        <v>231000000</v>
+      </c>
+      <c r="E42" s="3" t="n">
         <v>254000000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>244000000</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>265000000</v>
       </c>
       <c r="G42" s="3" t="n"/>
     </row>
@@ -2806,19 +3286,19 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>231000000</v>
+        <v>228000000</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>231000000</v>
       </c>
       <c r="D43" s="3" t="n">
+        <v>231000000</v>
+      </c>
+      <c r="E43" s="3" t="n">
         <v>254000000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>244000000</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>265000000</v>
       </c>
       <c r="G43" s="3" t="n"/>
     </row>
@@ -2829,19 +3309,19 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>2377000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>2355000000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>2400000000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>2380000000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>2335000000</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>2299000000</v>
       </c>
       <c r="G44" s="3" t="n"/>
     </row>
@@ -2852,19 +3332,19 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>3516000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>3569000000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>3604000000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>3524000000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>3463000000</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>3424000000</v>
       </c>
       <c r="G45" s="3" t="n"/>
     </row>
@@ -2875,19 +3355,19 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>2855000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>2881000000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>2871000000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>2818000000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>2724000000</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>2672000000</v>
       </c>
       <c r="G46" s="3" t="n"/>
     </row>
@@ -2898,19 +3378,19 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>661000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>688000000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>733000000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>706000000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>739000000</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>752000000</v>
       </c>
       <c r="G47" s="3" t="n"/>
     </row>
@@ -2921,19 +3401,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>661000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>688000000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>733000000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>706000000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>739000000</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>752000000</v>
       </c>
       <c r="G48" s="3" t="n"/>
     </row>
@@ -2944,19 +3424,19 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>10080000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>9972000000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>9745000000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>9280000000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>9278000000</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>9111000000</v>
       </c>
       <c r="G49" s="3" t="n"/>
     </row>
@@ -2967,19 +3447,19 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>5761000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>5377000000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>5138000000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>5393000000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>4871000000</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>4880000000</v>
       </c>
       <c r="G50" s="3" t="n"/>
     </row>
@@ -2990,19 +3470,19 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>15841000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>15349000000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>14883000000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>14673000000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>14149000000</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>13991000000</v>
       </c>
       <c r="G51" s="3" t="n"/>
     </row>
@@ -3013,19 +3493,19 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>15841000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>15349000000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>14883000000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>14673000000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>14149000000</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>13991000000</v>
       </c>
       <c r="G52" s="3" t="n"/>
     </row>
@@ -3034,7 +3514,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4544,7 +5024,1738 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G74"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>3940000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>3949000000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>3938000000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>3959998180</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>3960000000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>3940000000</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>3949000000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>3938000000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>3959998180</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>3960000000</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>24220000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>22628000000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>19689000000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>19747000000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>21118000000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>31303000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>30086000000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>28089000000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>28093000000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>29279000000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>-18281000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>-19818000000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>-20959000000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-21468000000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>-22732000000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>80164000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>77809000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>74962000000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>74936000000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>75214000000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>-2982000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>-1655000000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>-2575000000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-78000000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>-1679000000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>-18281000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>-19818000000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>-20959000000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-21468000000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-22732000000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>48861000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>47723000000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>46873000000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>46843000000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>45935000000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>68232000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>69090000000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>68237000000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>69704000000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>68792000000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>48861000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>47723000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>46873000000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>46843000000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>45935000000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>48861000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>47723000000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>46873000000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>46843000000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>45935000000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>-793000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>-836000000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>-930000000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-954000000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>-1133000000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-793000000</v>
+      </c>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n">
+        <v>-930000000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-954000000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-1133000000</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>-1493000000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>704000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>66000000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-364000000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>152000000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>48950000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>48493000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>48167000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>47747000000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>46916000000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>48950000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>48493000000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>48167000000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>47747000000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>46916000000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>76685000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>75648000000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>74229000000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>75448000000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>73847000000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>37144000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>38862000000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>38778000000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>40384000000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>39352000000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>3316000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>3167000000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>3074000000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>2995000000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>2711000000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Derivative Product Liabilities</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Tradeand Other Payables Non Current</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>2304000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>2124000000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>2172000000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>2165000000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>1874000000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>12153000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>12204000000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>12168000000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>12363000000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>11910000000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>12153000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>12204000000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>12168000000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>12363000000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>11910000000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>19371000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>21367000000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>21364000000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>22861000000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>22857000000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>19371000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>21367000000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>21364000000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>22861000000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>22857000000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>39541000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>36786000000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>35451000000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>35064000000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>34495000000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>4730000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>5417000000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>4972000000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>5420000000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>4701000000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>16446000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>16199000000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>15801000000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>16416000000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>16081000000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>16446000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>16199000000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>15801000000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>16416000000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>16081000000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>11932000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>8719000000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>6725000000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>5232000000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>6422000000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>11932000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>8719000000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>6725000000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>5232000000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>6422000000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>3498000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>3250000000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>3249000000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>1750000000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>2248000000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Commercial Paper</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>8434000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>5469000000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>3476000000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>3482000000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>4174000000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>3290000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>3494000000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>3064000000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>3611000000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>3210000000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>3143000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>2957000000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>4889000000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>4385000000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>4081000000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>3143000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>2957000000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>4889000000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>4385000000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>4081000000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>173000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>195000000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>2471000000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>1857000000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>1821000000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Income Tax Payable</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>173000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>195000000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>2471000000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>1857000000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>1821000000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>2970000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>2762000000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>2418000000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>2528000000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>2260000000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>125546000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>123371000000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>121102000000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>122291000000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>119782000000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>88987000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>88240000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>88226000000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>87305000000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>86966000000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>8068000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>7251000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>7113000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>6059000000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>5960000000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>7558000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>7399000000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>7314000000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>7356000000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>7016000000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>7558000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>7399000000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>7314000000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>7356000000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>7016000000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Non Current Note Receivables</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>3124000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>3157000000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>3075000000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>2876000000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>2896000000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Non Current Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>518000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>541000000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>644000000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>590000000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>351000000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>67142000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>67541000000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>67832000000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>68311000000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>68667000000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>7850000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>8307000000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>8713000000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>9175000000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>9643000000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>59292000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>59234000000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>59119000000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>59136000000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>59024000000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>2577000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>2351000000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>2248000000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>2113000000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>2076000000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>-7281000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>-7354000000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>-7413000000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>-7477000000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>-7444000000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>9858000000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>9705000000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>9661000000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>9590000000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>9520000000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>56000000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>49000000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>5670000000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>5594000000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>5550000000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>5494000000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>5474000000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>4132000000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>4060000000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>4062000000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>4045000000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>3996000000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>36559000000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>35131000000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>32876000000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>34986000000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>32816000000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>5795000000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>5884000000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>5833000000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>5950000000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>6107000000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>4708000000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>3920000000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>3395000000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>3164000000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>2832000000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Other Inventories</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>1107000000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>987000000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>985000000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>933000000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>919000000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>826000000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>684000000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>411000000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>261000000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>173000000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>2768000000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>2243000000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>1994000000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>1964000000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>1734000000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>9416000000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>9550000000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>7912000000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>9762000000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>8235000000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>352000000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>310000000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>371000000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>346000000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>622000000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Loans Receivable</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>2584000000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>2634000000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>2714000000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>2715000000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>2336000000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>6480000000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>6606000000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>4827000000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>6701000000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>5277000000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>-73000000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>-76000000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>-62000000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>-69000000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>-82000000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>6553000000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>6682000000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>4889000000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>6770000000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>5359000000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>16640000000</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>15777000000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>15736000000</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>16110000000</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>15642000000</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>9557000000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>8319000000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>7336000000</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>7764000000</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>7481000000</v>
+      </c>
+      <c r="G73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>7083000000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>7458000000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>8400000000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>8346000000</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>8161000000</v>
+      </c>
+      <c r="G74" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5790,13 +8001,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5806,6 +8017,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5816,30 +8028,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -5852,21 +8069,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>3343000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1539000000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>2889000000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>4017000000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>3796000000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>2031000000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5875,21 +8093,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-2612000000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-1079000000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>-2276000000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-1564000000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-2415000000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>-1075000000</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5898,21 +8117,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-4862000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-204000000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-2788000000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-3528000000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-7163000000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-6561000000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5921,21 +8141,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>6399000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>2682000000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>1559000000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>1904000000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>6982000000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>4674000000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5943,16 +8164,19 @@
           <t>Issuance Of Capital Stock</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n">
         <v>416000000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5961,21 +8185,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-414000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-283000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-323000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-217000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-261000000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>-210000000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5984,21 +8209,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>604000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>85000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>616000000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>130000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>601000000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>224000000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6007,21 +8233,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>659000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>2935000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>634000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>627000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>583000000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>2039000000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6030,21 +8257,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>7083000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>7459000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>8401000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>8910000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>8918000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>9508000000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6053,21 +8281,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>7459000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>8401000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>8910000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>8918000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>9508000000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>10208000000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6076,21 +8305,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-24000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-19000000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-14000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-20000000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-15000000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-18000000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6099,21 +8329,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>-352000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>-923000000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>-495000000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>12000000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>-575000000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>-682000000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6122,21 +8353,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-2039000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-1439000000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-3863000000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-3949000000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-5137000000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>-3945000000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6145,21 +8377,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-2039000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-1439000000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-3863000000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-3949000000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-5137000000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-3945000000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6168,21 +8401,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>1034000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-1065000000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-1000000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>577000000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>-654000000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6191,21 +8425,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-1617000000</v>
+        <v>-1660000000</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-1617000000</v>
       </c>
       <c r="D17" s="3" t="n">
+        <v>-1617000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
         <v>-1625000000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>-1627000000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>-1593000000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6214,21 +8449,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-1617000000</v>
+        <v>-1660000000</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>-1617000000</v>
       </c>
       <c r="D18" s="3" t="n">
+        <v>-1617000000</v>
+      </c>
+      <c r="E18" s="3" t="n">
         <v>-1625000000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-1627000000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>-1593000000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6237,21 +8473,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-2612000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>-725000000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>-2276000000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>-1148000000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-2415000000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>-755000000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6260,21 +8497,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-2612000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>-1079000000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>-2276000000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-1564000000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-2415000000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-1075000000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6282,16 +8520,19 @@
           <t>Common Stock Issuance</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n"/>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n">
         <v>416000000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="3" t="n"/>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6300,21 +8541,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>1199000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>1968000000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>31000000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-1176000000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-1672000000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>-943000000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6323,21 +8565,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-338000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-510000000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>1260000000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>448000000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-1491000000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>944000000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6346,21 +8589,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>1537000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>2478000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-1229000000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-1624000000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-181000000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>-1887000000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6369,21 +8613,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-4862000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-204000000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-2788000000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-3528000000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-7163000000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>-6561000000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6392,21 +8637,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>6399000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>2682000000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>1559000000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>1904000000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>6982000000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>4674000000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6415,21 +8661,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-2070000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-1306000000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>156000000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-273000000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>505000000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>1022000000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6438,21 +8685,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>-2070000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-1306000000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>156000000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>-273000000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>505000000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>1022000000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6461,21 +8709,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>14000000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-22000000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>14000000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-4000000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6484,21 +8733,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-1658000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-998000000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>508000000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-70000000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>800000000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>1276000000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6507,21 +8757,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>2115000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>1293000000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>2510000000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>1571000000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>1733000000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>1857000000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6530,21 +8781,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-3773000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-2291000000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>-2002000000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>-1641000000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>-933000000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>-581000000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6553,21 +8805,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-39000000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-7000000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>-34000000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>-40000000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6576,21 +8829,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>-39000000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>-7000000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>-34000000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>-40000000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6599,21 +8853,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>-414000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-283000000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>-323000000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-217000000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>-261000000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>-210000000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6622,21 +8877,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-414000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>-283000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>-323000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>-217000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-261000000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>-210000000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6645,21 +8901,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>3757000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>1822000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>3212000000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>4234000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>4057000000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>2241000000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6668,21 +8925,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>3757000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>1822000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>3212000000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>4234000000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>4057000000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>2241000000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6691,21 +8949,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>-753000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>-2810000000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>-1153000000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>525000000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>338000000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>-1831000000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6714,21 +8973,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>310000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>-1942000000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>-851000000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>935000000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>314000000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>-1063000000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6736,22 +8996,23 @@
           <t>Change In Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="3" t="n">
+      <c r="B41" s="3" t="n">
+        <v>-530000000</v>
+      </c>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n">
         <v>-374000000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>979000000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>-810000000</v>
       </c>
-      <c r="F41" s="3" t="n">
+      <c r="G41" s="3" t="n">
         <v>-13000000</v>
       </c>
-      <c r="G41" s="3" t="n">
-        <v>37000000</v>
-      </c>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6760,21 +9021,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>-50000000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>-592000000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>17000000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>-89000000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>-237000000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6783,21 +9045,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>-4000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>763000000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>-647000000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>645000000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>211000000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>371000000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6806,21 +9069,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>-212000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>419000000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>-539000000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>378000000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>-138000000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>461000000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6829,21 +9093,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>208000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>344000000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>-108000000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>267000000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>349000000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>-90000000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6852,21 +9117,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>208000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>344000000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>-108000000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>267000000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>349000000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>-90000000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6875,21 +9141,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>-788000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>-527000000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>-234000000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>-332000000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>100000000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>212000000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6898,21 +9165,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>219000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>-1611000000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>1545000000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>-1719000000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>612000000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>-1101000000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6921,21 +9189,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>133000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>-1803000000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>1857000000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>-1428000000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>437000000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>-1258000000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6944,13 +9213,14 @@
         </is>
       </c>
       <c r="B50" s="3" t="n"/>
-      <c r="C50" s="3" t="n">
+      <c r="C50" s="3" t="n"/>
+      <c r="D50" s="3" t="n">
         <v>-3000000</v>
       </c>
-      <c r="D50" s="3" t="n"/>
       <c r="E50" s="3" t="n"/>
       <c r="F50" s="3" t="n"/>
-      <c r="G50" s="3" t="n">
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n">
         <v>-1000000</v>
       </c>
     </row>
@@ -6961,21 +9231,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>914000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>934000000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>1055000000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>948000000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>945000000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>921000000</v>
-      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6983,18 +9254,21 @@
           <t>Provisionand Write Offof Assets</t>
         </is>
       </c>
-      <c r="B52" s="3" t="n"/>
+      <c r="B52" s="3" t="n">
+        <v>2000000</v>
+      </c>
       <c r="C52" s="3" t="n"/>
-      <c r="D52" s="3" t="n">
+      <c r="D52" s="3" t="n"/>
+      <c r="E52" s="3" t="n">
         <v>7000000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>10000000</v>
       </c>
-      <c r="F52" s="3" t="n">
+      <c r="G52" s="3" t="n">
         <v>8000000</v>
       </c>
-      <c r="G52" s="3" t="n">
+      <c r="H52" s="3" t="n">
         <v>-1000000</v>
       </c>
     </row>
@@ -7005,21 +9279,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>-153000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>-89000000</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>25000000</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>-341000000</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="F53" s="3" t="n">
         <v>-410000000</v>
       </c>
-      <c r="F53" s="3" t="n">
-        <v>-101000000</v>
-      </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7028,21 +9303,22 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
+        <v>-153000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>-89000000</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>25000000</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>-341000000</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="F54" s="3" t="n">
         <v>-410000000</v>
       </c>
-      <c r="F54" s="3" t="n">
-        <v>-101000000</v>
-      </c>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7051,21 +9327,22 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
+        <v>637000000</v>
+      </c>
+      <c r="C55" s="3" t="n">
         <v>659000000</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="D55" s="3" t="n">
         <v>606000000</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>635000000</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="F55" s="3" t="n">
         <v>626000000</v>
       </c>
-      <c r="F55" s="3" t="n">
-        <v>761000000</v>
-      </c>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7074,21 +9351,22 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
+        <v>637000000</v>
+      </c>
+      <c r="C56" s="3" t="n">
         <v>659000000</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="D56" s="3" t="n">
         <v>606000000</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="E56" s="3" t="n">
         <v>635000000</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="F56" s="3" t="n">
         <v>626000000</v>
       </c>
-      <c r="F56" s="3" t="n">
-        <v>761000000</v>
-      </c>
       <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7096,22 +9374,23 @@
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="3" t="n">
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n">
         <v>659000000</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="D57" s="3" t="n">
         <v>606000000</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="E57" s="3" t="n">
         <v>635000000</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="F57" s="3" t="n">
         <v>626000000</v>
       </c>
-      <c r="F57" s="3" t="n">
+      <c r="G57" s="3" t="n">
         <v>761000000</v>
       </c>
-      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7120,21 +9399,22 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
+        <v>-263000000</v>
+      </c>
+      <c r="C58" s="3" t="n">
         <v>-59000000</v>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="D58" s="3" t="n">
         <v>-178000000</v>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="E58" s="3" t="n">
         <v>-90000000</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="F58" s="3" t="n">
         <v>57000000</v>
       </c>
-      <c r="F58" s="3" t="n">
-        <v>55000000</v>
-      </c>
       <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7143,21 +9423,22 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
+        <v>-263000000</v>
+      </c>
+      <c r="C59" s="3" t="n">
         <v>-59000000</v>
       </c>
-      <c r="C59" s="3" t="n">
+      <c r="D59" s="3" t="n">
         <v>-178000000</v>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="E59" s="3" t="n">
         <v>-90000000</v>
       </c>
-      <c r="E59" s="3" t="n">
+      <c r="F59" s="3" t="n">
         <v>57000000</v>
       </c>
-      <c r="F59" s="3" t="n">
-        <v>55000000</v>
-      </c>
       <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7166,28 +9447,29 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
+        <v>3373000000</v>
+      </c>
+      <c r="C60" s="3" t="n">
         <v>3175000000</v>
       </c>
-      <c r="C60" s="3" t="n">
+      <c r="D60" s="3" t="n">
         <v>2860000000</v>
       </c>
-      <c r="D60" s="3" t="n">
+      <c r="E60" s="3" t="n">
         <v>2550000000</v>
       </c>
-      <c r="E60" s="3" t="n">
+      <c r="F60" s="3" t="n">
         <v>2491000000</v>
       </c>
-      <c r="F60" s="3" t="n">
-        <v>2428000000</v>
-      </c>
       <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
